--- a/sheets/대금율보/검수/연인.xlsx
+++ b/sheets/대금율보/검수/연인.xlsx
@@ -6651,7 +6651,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –無</t>
         </is>
       </c>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –林</t>
         </is>
       </c>
@@ -6671,7 +6671,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹汰</t>
         </is>
       </c>
@@ -6719,7 +6719,7 @@
       <c r="S4" s="23"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –浹</t>
         </is>
       </c>
@@ -6769,7 +6769,7 @@
       <c r="O5" s="23"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
@@ -6818,7 +6818,7 @@
       <c r="K6" s="26"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋湳</t>
         </is>
       </c>
@@ -6919,7 +6919,7 @@
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -6971,14 +6971,14 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –林</t>
         </is>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –林</t>
         </is>
       </c>
@@ -7024,7 +7024,7 @@
       <c r="S8" s="23"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –林</t>
         </is>
       </c>
@@ -7055,7 +7055,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 –淋</t>
         </is>
       </c>
@@ -7127,7 +7127,7 @@
       <c r="I10" s="26"/>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㶂淋</t>
         </is>
       </c>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –仲</t>
         </is>
       </c>
@@ -7294,7 +7294,7 @@
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹‹
+          <t xml:space="preserve">浹
 –汰</t>
         </is>
       </c>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –林</t>
         </is>
       </c>
@@ -7329,7 +7329,7 @@
       <c r="S12" s="23"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
@@ -7349,7 +7349,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹‹
+          <t xml:space="preserve">浹
 –湳</t>
         </is>
       </c>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㽔‹
+          <t xml:space="preserve">㽔
 –林</t>
         </is>
       </c>
@@ -7403,7 +7403,7 @@
         <is>
           <t xml:space="preserve">太
 林
-南‹</t>
+南</t>
         </is>
       </c>
       <c r="C14" s="27"/>
@@ -7426,7 +7426,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="26" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –汰</t>
         </is>
       </c>
@@ -7588,7 +7588,7 @@
       <c r="G16" s="23"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –無</t>
         </is>
       </c>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –林</t>
         </is>
       </c>
@@ -7651,7 +7651,7 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–南‹</t>
+–南</t>
         </is>
       </c>
       <c r="G17" s="23"/>
@@ -7659,7 +7659,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㽔‹
+          <t xml:space="preserve">㽔
 –林</t>
         </is>
       </c>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 無
 潢</t>
         </is>
@@ -7753,7 +7753,7 @@
       <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–‹
+–
 林ʒ</t>
         </is>
       </c>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="R19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –林</t>
         </is>
       </c>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="T21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㽔‹
+          <t xml:space="preserve">㽔
 –林</t>
         </is>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="G22" s="26"/>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –林ʒ</t>
         </is>
       </c>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –㳞</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/연인.xlsx
+++ b/sheets/대금율보/검수/연인.xlsx
@@ -6504,32 +6504,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -6783,7 +6783,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="26"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -7397,7 +7397,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="24" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="96.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="96.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="96.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="96.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="96.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="96.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="24" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="96.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="96.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -8138,6 +8138,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="37"/>
 </worksheet>
 </file>